--- a/artfynd/A 14597-2020 artfynd.xlsx
+++ b/artfynd/A 14597-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14597-2020 artfynd.xlsx
+++ b/artfynd/A 14597-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1789,6 +1789,254 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123329316</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56821</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>sträckande O</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Eslövs kommun, Götaland, Tallbacksvägen, Kungshult, Stavröd, Skåne län, Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>399644</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6191002</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Eslöv</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Eslöv</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jonny Johansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jonny Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123329321</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57848</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Eslövs kommun, Götaland, Tallbacksvägen, Kungshult, Stavröd, Skåne län, Sk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>399644</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6191002</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Eslöv</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Eslöv</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jonny Johansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jonny Johansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14597-2020 artfynd.xlsx
+++ b/artfynd/A 14597-2020 artfynd.xlsx
@@ -1794,7 +1794,7 @@
         <v>123329316</v>
       </c>
       <c r="B11" t="n">
-        <v>56821</v>
+        <v>56824</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>123329321</v>
       </c>
       <c r="B12" t="n">
-        <v>57848</v>
+        <v>57851</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 14597-2020 artfynd.xlsx
+++ b/artfynd/A 14597-2020 artfynd.xlsx
@@ -1791,10 +1791,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123329316</v>
+        <v>123329321</v>
       </c>
       <c r="B11" t="n">
-        <v>56824</v>
+        <v>57851</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1807,16 +1807,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100065</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>sträckande O</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1915,10 +1915,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123329321</v>
+        <v>123329316</v>
       </c>
       <c r="B12" t="n">
-        <v>57851</v>
+        <v>56824</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1931,16 +1931,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>100065</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1950,14 +1950,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>sträckande O</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 14597-2020 artfynd.xlsx
+++ b/artfynd/A 14597-2020 artfynd.xlsx
@@ -1794,7 +1794,7 @@
         <v>123329321</v>
       </c>
       <c r="B11" t="n">
-        <v>57851</v>
+        <v>57857</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>123329316</v>
       </c>
       <c r="B12" t="n">
-        <v>56824</v>
+        <v>56830</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 14597-2020 artfynd.xlsx
+++ b/artfynd/A 14597-2020 artfynd.xlsx
@@ -1794,7 +1794,7 @@
         <v>123329321</v>
       </c>
       <c r="B11" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>123329316</v>
       </c>
       <c r="B12" t="n">
-        <v>56830</v>
+        <v>56833</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 14597-2020 artfynd.xlsx
+++ b/artfynd/A 14597-2020 artfynd.xlsx
@@ -1794,7 +1794,7 @@
         <v>123329321</v>
       </c>
       <c r="B11" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>123329316</v>
       </c>
       <c r="B12" t="n">
-        <v>56833</v>
+        <v>56834</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 14597-2020 artfynd.xlsx
+++ b/artfynd/A 14597-2020 artfynd.xlsx
@@ -1791,10 +1791,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123329321</v>
+        <v>123329316</v>
       </c>
       <c r="B11" t="n">
-        <v>57861</v>
+        <v>56834</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1807,16 +1807,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>100065</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>sträckande O</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1915,10 +1915,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123329316</v>
+        <v>123329321</v>
       </c>
       <c r="B12" t="n">
-        <v>56834</v>
+        <v>57861</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1931,16 +1931,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100065</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1950,14 +1950,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>sträckande O</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
